--- a/VerveStacks_ITA/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5DF06E4-7870-43AC-B3C4-5D0C15C46E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A4FC46-0619-4AD7-96D4-DAEE78EB53B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ITA/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A4FC46-0619-4AD7-96D4-DAEE78EB53B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8085E249-B913-4D0F-8B60-01876D8CCA86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ITA/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8085E249-B913-4D0F-8B60-01876D8CCA86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E29C743-2BCB-4855-A257-262730180F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ITA/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E29C743-2BCB-4855-A257-262730180F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B39B3EF-AFE5-455D-ABAE-E2EC6D39DC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_ITA/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B39B3EF-AFE5-455D-ABAE-E2EC6D39DC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8646497-EF45-41CD-B29D-60F89253B58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
